--- a/auto OMS Python/engines/shopee/media_chihuy1984.xlsx
+++ b/auto OMS Python/engines/shopee/media_chihuy1984.xlsx
@@ -750,6 +750,75 @@
     <t>50Bộ  8mmx60mm+ Vít</t>
   </si>
   <si>
+    <t>14815890188</t>
+  </si>
+  <si>
+    <t>Kẹp Cố Định Dây Điện, Cáp Mạng K114 – Keo Nano Siêu Dính, Không Cần Khoan</t>
+  </si>
+  <si>
+    <t>100279 - Mobile &amp; Gadgets/Accessories/Phone Grips</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/5f95c8adb4840a737864e1f8db5a93a6</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/faae7dd8cc4f46dfa22a40af3968b27e</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/81052f2c67b89bdff09e54ea773831eb</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/8d1839dabfaf83ad8cb972103ecd831e</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/0baf454fc8a04cd42449c1fea18c8a13</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/9edf17f4143a09259c70babbede7153a</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/c5296c147cf67ab7648b65c4b616ee36</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/8eb2447ad49bf498f8ed4f8caf07c900</t>
+  </si>
+  <si>
+    <t>10 Kẹp Trắng 12mm</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7ras8-mbnv4lokm5xq5f</t>
+  </si>
+  <si>
+    <t>10 Kẹp Trắng 16mm</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-lyrxgjruosyp4b</t>
+  </si>
+  <si>
+    <t>10 Kẹp Trắng 22mm</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-lyrxgnkn37t905</t>
+  </si>
+  <si>
+    <t>10 Kẹp Đen 12mm</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-lyrxftit2clp2a</t>
+  </si>
+  <si>
+    <t>10 Kẹp Đen 16mm</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-lyrxfvndyaht5d</t>
+  </si>
+  <si>
+    <t>10 Kẹp Đen 22mm</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-lyrxgca5m2e9bb</t>
+  </si>
+  <si>
     <t>12455764340</t>
   </si>
   <si>
@@ -795,75 +864,6 @@
     <t>https://cf.shopee.vn/file/5d30f4cd91b2bda195a900e2872049b4</t>
   </si>
   <si>
-    <t>14815890188</t>
-  </si>
-  <si>
-    <t>Kẹp Cố Định Dây Điện, Cáp Mạng K114 – Keo Nano Siêu Dính, Không Cần Khoan</t>
-  </si>
-  <si>
-    <t>100279 - Mobile &amp; Gadgets/Accessories/Phone Grips</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/5f95c8adb4840a737864e1f8db5a93a6</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/faae7dd8cc4f46dfa22a40af3968b27e</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/81052f2c67b89bdff09e54ea773831eb</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/8d1839dabfaf83ad8cb972103ecd831e</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/0baf454fc8a04cd42449c1fea18c8a13</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/9edf17f4143a09259c70babbede7153a</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/c5296c147cf67ab7648b65c4b616ee36</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/8eb2447ad49bf498f8ed4f8caf07c900</t>
-  </si>
-  <si>
-    <t>10 Kẹp Trắng 12mm</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7ras8-mbnv4lokm5xq5f</t>
-  </si>
-  <si>
-    <t>10 Kẹp Trắng 16mm</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-lyrxgjruosyp4b</t>
-  </si>
-  <si>
-    <t>10 Kẹp Trắng 22mm</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-lyrxgnkn37t905</t>
-  </si>
-  <si>
-    <t>10 Kẹp Đen 12mm</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-lyrxftit2clp2a</t>
-  </si>
-  <si>
-    <t>10 Kẹp Đen 16mm</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-lyrxfvndyaht5d</t>
-  </si>
-  <si>
-    <t>10 Kẹp Đen 22mm</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-lyrxgca5m2e9bb</t>
-  </si>
-  <si>
     <t>24418368117</t>
   </si>
   <si>
@@ -1395,6 +1395,33 @@
     <t>https://cf.shopee.vn/file/vn-11134207-7ra0g-m9zj2ygo4bb84e</t>
   </si>
   <si>
+    <t>24768421006</t>
+  </si>
+  <si>
+    <t>COMBO 20 Tắc Kê Sắt + 20 Vít Chịu Lực Cực Tốt Không Sợ Bung Và Rơi Rớt Mọi Vật Dụng Treo Tường Sau Khi Lắp Đặt K243</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7ra0g-m79divt25918d2</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-820l4-mhpp92qzl1xg55</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-820l4-mhppa4nlk54xc5</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-820l4-mhppboebnqbo6b</t>
+  </si>
+  <si>
+    <t>20 Bộ KT 5mm X 30mm</t>
+  </si>
+  <si>
+    <t>20 Bộ KT 6mm X 32mm</t>
+  </si>
+  <si>
+    <t>20 Bộ KT 8mm X 60mm</t>
+  </si>
+  <si>
     <t>5948362499</t>
   </si>
   <si>
@@ -1497,6 +1524,36 @@
     <t>https://cf.shopee.vn/file/1c536bba9decbe5e786e89d95e2fd3db</t>
   </si>
   <si>
+    <t>13615381825</t>
+  </si>
+  <si>
+    <t>Bộ 100 Đinh 2 Đầu Dùng Để Đóng Chân Tường ,Tủ Kệ Bếp Che Khuyết Điểm K97</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-ltdi26v6bxjtca</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-ltdi26v5zafte1</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-ltdi26v66ba1d9</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-ltdi26v6eqpw1a</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-ltdi26v5zah0ef</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-ltdi26w9xo04c9</t>
+  </si>
+  <si>
+    <t>Bộ 100 Đinh + ống</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-ltdi26v6hjtlac</t>
+  </si>
+  <si>
     <t>6856001620</t>
   </si>
   <si>
@@ -1674,36 +1731,6 @@
     <t>https://cf.shopee.vn/file/vn-11134207-7r98o-lphqdrvv80mn99</t>
   </si>
   <si>
-    <t>13615381825</t>
-  </si>
-  <si>
-    <t>Bộ 100 Đinh 2 Đầu Dùng Để Đóng Chân Tường ,Tủ Kệ Bếp Che Khuyết Điểm K97</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-ltdi26v6bxjtca</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-ltdi26v5zafte1</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-ltdi26v66ba1d9</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-ltdi26v6eqpw1a</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-ltdi26v5zah0ef</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-ltdi26w9xo04c9</t>
-  </si>
-  <si>
-    <t>Bộ 100 Đinh + ống</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7r98o-ltdi26v6hjtlac</t>
-  </si>
-  <si>
     <t>7756001691</t>
   </si>
   <si>
@@ -1854,33 +1881,6 @@
     <t>https://cf.shopee.vn/file/sg-11134201-22120-ufito54g0ukve8</t>
   </si>
   <si>
-    <t>24768421006</t>
-  </si>
-  <si>
-    <t>COMBO 20 Tắc Kê Sắt + 20 Vít Chịu Lực Cực Tốt Không Sợ Bung Và Rơi Rớt Mọi Vật Dụng Treo Tường Sau Khi Lắp Đặt K243</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7ra0g-m79divt25918d2</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-820l4-mhpp92qzl1xg55</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-820l4-mhppa4nlk54xc5</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-820l4-mhppboebnqbo6b</t>
-  </si>
-  <si>
-    <t>20 Bộ KT 5mm X 30mm</t>
-  </si>
-  <si>
-    <t>20 Bộ KT 6mm X 32mm</t>
-  </si>
-  <si>
-    <t>20 Bộ KT 8mm X 60mm</t>
-  </si>
-  <si>
     <t>9523434925</t>
   </si>
   <si>
@@ -3435,6 +3435,48 @@
     <t>https://cf.shopee.vn/file/vn-11134207-820l4-mfdltiw13jt61a</t>
   </si>
   <si>
+    <t>13840948033</t>
+  </si>
+  <si>
+    <t>Khung Lọc Rác Dính Nano K98 – Dán Gọn Thành Bồn, Ngăn Rác Hiệu Quả, Dễ Gắn Túi Lưới</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/a05809c4cf63e8b2d9432d79644a9292</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/c9f085b33ae7419bd44d5cd042482483</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/a6e3691efc8ac2225f5a1e422c358937</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/2a6d6755dc5710d8229c50cb33a13070</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/9174166802fde6e1745416bff9ed9e47</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/4175369fc5c2c6972818884692789d57</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/65d37f09517639d6cce7c6717ebaeebc</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/813f26645d5c8f904c1e0b28bf00fa41</t>
+  </si>
+  <si>
+    <t>Khung Xám + 50 TÚI</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7ra0g-m7j8i1chcqpfbf</t>
+  </si>
+  <si>
+    <t>Khung Xanh + 50 TÚI</t>
+  </si>
+  <si>
+    <t>https://cf.shopee.vn/file/vn-11134207-7ra0g-m7j8i3f4cx6k78</t>
+  </si>
+  <si>
     <t>8088637510</t>
   </si>
   <si>
@@ -3478,48 +3520,6 @@
   </si>
   <si>
     <t>https://cf.shopee.vn/file/vn-11134207-7ra0g-m6dc80ji95iu7b</t>
-  </si>
-  <si>
-    <t>13840948033</t>
-  </si>
-  <si>
-    <t>Khung Lọc Rác Dính Nano K98 – Dán Gọn Thành Bồn, Ngăn Rác Hiệu Quả, Dễ Gắn Túi Lưới</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/a05809c4cf63e8b2d9432d79644a9292</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/c9f085b33ae7419bd44d5cd042482483</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/a6e3691efc8ac2225f5a1e422c358937</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/2a6d6755dc5710d8229c50cb33a13070</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/9174166802fde6e1745416bff9ed9e47</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/4175369fc5c2c6972818884692789d57</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/65d37f09517639d6cce7c6717ebaeebc</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/813f26645d5c8f904c1e0b28bf00fa41</t>
-  </si>
-  <si>
-    <t>Khung Xám + 50 TÚI</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7ra0g-m7j8i1chcqpfbf</t>
-  </si>
-  <si>
-    <t>Khung Xanh + 50 TÚI</t>
-  </si>
-  <si>
-    <t>https://cf.shopee.vn/file/vn-11134207-7ra0g-m7j8i3f4cx6k78</t>
   </si>
   <si>
     <t>12460878593</t>
@@ -6186,30 +6186,48 @@
       <c r="L18" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>255</v>
-      </c>
+      <c r="M18" s="3"/>
       <c r="N18" s="10"/>
       <c r="O18" s="10"/>
       <c r="P18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="R18" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="Q18" s="2" t="s">
+      <c r="S18" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="R18" s="3" t="s">
+      <c r="T18" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10"/>
-      <c r="U18" s="10"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="10"/>
-      <c r="Y18" s="10"/>
-      <c r="Z18" s="10"/>
-      <c r="AA18" s="10"/>
-      <c r="AB18" s="10"/>
+      <c r="U18" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="AA18" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="AB18" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="AC18" s="10"/>
       <c r="AD18" s="10"/>
       <c r="AE18" s="10"/>
@@ -6222,81 +6240,63 @@
     </row>
     <row customHeight="true" ht="15" r="19">
       <c r="A19" s="1" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="M19" s="3"/>
+        <v>277</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>278</v>
+      </c>
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
       <c r="P19" s="2" t="s">
-        <v>103</v>
+        <v>279</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="U19" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="V19" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="W19" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="X19" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="Y19" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="Z19" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="AA19" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="AB19" s="3" t="s">
         <v>281</v>
       </c>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="10"/>
+      <c r="AA19" s="10"/>
+      <c r="AB19" s="10"/>
       <c r="AC19" s="10"/>
       <c r="AD19" s="10"/>
       <c r="AE19" s="10"/>
@@ -6586,7 +6586,7 @@
         <v>337</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>338</v>
@@ -7215,26 +7215,22 @@
         <v>460</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="G33" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="H33" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>467</v>
-      </c>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
@@ -7244,29 +7240,25 @@
         <v>103</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="W33" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>475</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="W33" s="10"/>
+      <c r="X33" s="10"/>
       <c r="Y33" s="10"/>
       <c r="Z33" s="10"/>
       <c r="AA33" s="10"/>
@@ -7283,45 +7275,65 @@
     </row>
     <row customHeight="true" ht="15" r="34">
       <c r="A34" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="J34" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="10"/>
       <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="10"/>
-      <c r="S34" s="10"/>
-      <c r="T34" s="10"/>
-      <c r="U34" s="10"/>
-      <c r="V34" s="10"/>
-      <c r="W34" s="10"/>
-      <c r="X34" s="10"/>
+      <c r="P34" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="V34" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="X34" s="3" t="s">
+        <v>484</v>
+      </c>
       <c r="Y34" s="10"/>
       <c r="Z34" s="10"/>
       <c r="AA34" s="10"/>
@@ -7338,32 +7350,30 @@
     </row>
     <row customHeight="true" ht="15" r="35">
       <c r="A35" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="I35" s="3" t="s">
         <v>492</v>
       </c>
+      <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
@@ -7404,22 +7414,22 @@
         <v>495</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>198</v>
+        <v>496</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
@@ -7427,27 +7437,13 @@
       <c r="M36" s="3"/>
       <c r="N36" s="10"/>
       <c r="O36" s="10"/>
-      <c r="P36" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="Q36" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="R36" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="S36" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="T36" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="U36" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="V36" s="3" t="s">
-        <v>505</v>
-      </c>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="10"/>
+      <c r="T36" s="10"/>
+      <c r="U36" s="10"/>
+      <c r="V36" s="10"/>
       <c r="W36" s="10"/>
       <c r="X36" s="10"/>
       <c r="Y36" s="10"/>
@@ -7466,32 +7462,32 @@
     </row>
     <row customHeight="true" ht="15" r="37">
       <c r="A37" s="1" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="I37" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="J37" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>514</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
@@ -7502,17 +7498,13 @@
         <v>103</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="R37" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="S37" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="T37" s="3" t="s">
-        <v>510</v>
-      </c>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
       <c r="U37" s="10"/>
       <c r="V37" s="10"/>
       <c r="W37" s="10"/>
@@ -7533,59 +7525,59 @@
     </row>
     <row customHeight="true" ht="15" r="38">
       <c r="A38" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="H38" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="I38" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>527</v>
-      </c>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
       <c r="N38" s="10"/>
       <c r="O38" s="10"/>
       <c r="P38" s="2" t="s">
-        <v>103</v>
+        <v>520</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>528</v>
+        <v>207</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="U38" s="10"/>
-      <c r="V38" s="10"/>
+        <v>523</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="V38" s="3" t="s">
+        <v>524</v>
+      </c>
       <c r="W38" s="10"/>
       <c r="X38" s="10"/>
       <c r="Y38" s="10"/>
@@ -7604,73 +7596,57 @@
     </row>
     <row customHeight="true" ht="15" r="39">
       <c r="A39" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="I39" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="J39" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>543</v>
-      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
       <c r="N39" s="10"/>
       <c r="O39" s="10"/>
       <c r="P39" s="2" t="s">
         <v>103</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="T39" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="U39" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="V39" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="W39" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="X39" s="3" t="s">
-        <v>551</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="U39" s="10"/>
+      <c r="V39" s="10"/>
+      <c r="W39" s="10"/>
+      <c r="X39" s="10"/>
       <c r="Y39" s="10"/>
       <c r="Z39" s="10"/>
       <c r="AA39" s="10"/>
@@ -7687,34 +7663,38 @@
     </row>
     <row customHeight="true" ht="15" r="40">
       <c r="A40" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="B40" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>537</v>
+      </c>
       <c r="C40" s="2" t="s">
-        <v>553</v>
+        <v>538</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>137</v>
+        <v>539</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="K40" s="3"/>
+        <v>545</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>546</v>
+      </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="10"/>
@@ -7723,13 +7703,17 @@
         <v>103</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="S40" s="10"/>
-      <c r="T40" s="10"/>
+        <v>546</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="T40" s="3" t="s">
+        <v>549</v>
+      </c>
       <c r="U40" s="10"/>
       <c r="V40" s="10"/>
       <c r="W40" s="10"/>
@@ -7750,66 +7734,72 @@
     </row>
     <row customHeight="true" ht="15" r="41">
       <c r="A41" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="M41" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
       <c r="N41" s="10"/>
       <c r="O41" s="10"/>
       <c r="P41" s="2" t="s">
-        <v>256</v>
+        <v>103</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="T41" s="3" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="Y41" s="10"/>
       <c r="Z41" s="10"/>
@@ -7827,55 +7817,67 @@
     </row>
     <row customHeight="true" ht="15" r="42">
       <c r="A42" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J42" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>591</v>
-      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
       <c r="N42" s="10"/>
       <c r="O42" s="10"/>
-      <c r="P42" s="10"/>
-      <c r="Q42" s="10"/>
-      <c r="R42" s="10"/>
-      <c r="S42" s="10"/>
-      <c r="T42" s="10"/>
-      <c r="U42" s="10"/>
-      <c r="V42" s="10"/>
-      <c r="W42" s="10"/>
-      <c r="X42" s="10"/>
+      <c r="P42" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="U42" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>587</v>
+      </c>
       <c r="Y42" s="10"/>
       <c r="Z42" s="10"/>
       <c r="AA42" s="10"/>
@@ -7892,49 +7894,49 @@
     </row>
     <row customHeight="true" ht="15" r="43">
       <c r="A43" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="F43" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="G43" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E43" s="3" t="s">
+      <c r="H43" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="I43" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="J43" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="K43" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="L43" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="M43" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
       <c r="N43" s="10"/>
       <c r="O43" s="10"/>
-      <c r="P43" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q43" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>602</v>
-      </c>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
       <c r="S43" s="10"/>
       <c r="T43" s="10"/>
       <c r="U43" s="10"/>
@@ -7957,31 +7959,35 @@
     </row>
     <row customHeight="true" ht="15" r="44">
       <c r="A44" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="E44" s="3" t="s">
+      <c r="F44" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="G44" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="H44" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="I44" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="J44" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
@@ -8025,7 +8031,7 @@
         <v>613</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>137</v>
+        <v>488</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>614</v>
@@ -8039,7 +8045,9 @@
       <c r="H45" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="I45" s="3"/>
+      <c r="I45" s="3" t="s">
+        <v>618</v>
+      </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
@@ -8050,23 +8058,15 @@
         <v>103</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="S45" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="U45" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>617</v>
-      </c>
+      <c r="S45" s="10"/>
+      <c r="T45" s="10"/>
+      <c r="U45" s="10"/>
+      <c r="V45" s="10"/>
       <c r="W45" s="10"/>
       <c r="X45" s="10"/>
       <c r="Y45" s="10"/>
@@ -8149,7 +8149,7 @@
         <v>631</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>632</v>
@@ -8849,7 +8849,7 @@
       <c r="N57" s="10"/>
       <c r="O57" s="10"/>
       <c r="P57" s="2" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="Q57" s="2" t="s">
         <v>768</v>
@@ -8987,7 +8987,7 @@
       <c r="N59" s="10"/>
       <c r="O59" s="10"/>
       <c r="P59" s="2" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="Q59" s="2" t="s">
         <v>795</v>
@@ -9265,7 +9265,7 @@
       <c r="N63" s="10"/>
       <c r="O63" s="10"/>
       <c r="P63" s="2" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="Q63" s="2" t="s">
         <v>852</v>
@@ -9428,7 +9428,7 @@
         <v>876</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>877</v>
@@ -10985,7 +10985,7 @@
         <v>1140</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>1104</v>
+        <v>639</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>1141</v>
@@ -11011,25 +11011,23 @@
       <c r="L89" s="3" t="s">
         <v>1148</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>1149</v>
-      </c>
+      <c r="M89" s="3"/>
       <c r="N89" s="10"/>
       <c r="O89" s="10"/>
       <c r="P89" s="2" t="s">
         <v>103</v>
       </c>
       <c r="Q89" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="R89" s="3" t="s">
         <v>1150</v>
       </c>
-      <c r="R89" s="3" t="s">
+      <c r="S89" s="2" t="s">
         <v>1151</v>
       </c>
-      <c r="S89" s="2" t="s">
+      <c r="T89" s="3" t="s">
         <v>1152</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>1153</v>
       </c>
       <c r="U89" s="10"/>
       <c r="V89" s="10"/>
@@ -11051,40 +11049,42 @@
     </row>
     <row customHeight="true" ht="15" r="90">
       <c r="A90" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>1155</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="E90" s="3" t="s">
+      <c r="F90" s="3" t="s">
         <v>1156</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="G90" s="3" t="s">
         <v>1157</v>
       </c>
-      <c r="G90" s="3" t="s">
+      <c r="H90" s="3" t="s">
         <v>1158</v>
       </c>
-      <c r="H90" s="3" t="s">
+      <c r="I90" s="3" t="s">
         <v>1159</v>
       </c>
-      <c r="I90" s="3" t="s">
+      <c r="J90" s="3" t="s">
         <v>1160</v>
       </c>
-      <c r="J90" s="3" t="s">
+      <c r="K90" s="3" t="s">
         <v>1161</v>
       </c>
-      <c r="K90" s="3" t="s">
+      <c r="L90" s="3" t="s">
         <v>1162</v>
       </c>
-      <c r="L90" s="3" t="s">
+      <c r="M90" s="3" t="s">
         <v>1163</v>
       </c>
-      <c r="M90" s="3"/>
       <c r="N90" s="10"/>
       <c r="O90" s="10"/>
       <c r="P90" s="2" t="s">
@@ -11129,7 +11129,7 @@
         <v>1169</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>1170</v>
@@ -11277,7 +11277,7 @@
         <v>1196</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>1146</v>
+        <v>1160</v>
       </c>
       <c r="K93" s="3" t="s">
         <v>1197</v>
